--- a/data/trans_camb/IP19C03-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-7.374042347570409</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.836783675800266</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.795082903778765</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.034840836168686</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-5.57485190418282</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.487973681782387</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-16.303141312805</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-16.39474634150805</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-13.56010528093739</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-10.01898317587229</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-11.65000461110153</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-10.70722750192483</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>2.161123366218073</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.94936451754336</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.380940986466494</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>15.74946139177468</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.4602086949896586</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>8.381992891488343</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.2777180872308661</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.182160916289734</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.1606482904315014</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.0861361161057162</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.222349253973207</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.05934683894075153</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.5159096325767925</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.5521623275995666</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.4643610349568287</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.3646009314691204</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4026397523503857</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3899995342844315</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.1190035418704583</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.5119643635040331</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.2391348432425736</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.8116352204284006</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.02796426416080591</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3679433182723121</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-0.3686494925977474</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-7.508548729617447</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.669119731881774</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-4.775668995409149</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-2.599556200758244</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-6.233873404170262</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-9.109726822591421</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-15.73276750385334</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-13.87633349246351</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-13.31444562325684</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-8.775658382270695</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-12.63993436252994</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>10.05750638845877</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1169423829433596</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.449844498598281</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.069848041367532</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>4.372891512528364</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-0.623105202124992</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.01891295770840959</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.3852137800979983</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.2383402351482959</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.2437791568256711</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1330445054086271</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3190477680751474</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.3932878317317096</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.6548211939611916</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.5738649752767414</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.5493967693771353</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3872955488867031</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5471522062435065</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.6818567500369331</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.04591109856747837</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.2739027088248224</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.265840065615343</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2423820130934883</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.024549376684703</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>2.662939311351631</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.7774246402703577</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-4.940991647753856</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-5.908857306348176</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-1.035996592720917</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-3.331661018511065</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-6.415376363031173</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-8.587490287415129</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-15.43540603383756</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-15.51103533234408</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-7.625608543483136</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-9.581698089625256</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>12.08729577291053</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.858756768029771</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.076207515172698</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.392995874267308</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>5.382862749935617</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.154399355401834</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.1854556423806736</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.05414234768674575</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.2374760100889452</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.2839939747589673</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.05924925030564347</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1905396398079598</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.3894950830637783</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.4429658078331859</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.5873292578423536</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.5896012036471031</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.3707540981549722</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.4585026495942852</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>1.200039406716159</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.7436807936628432</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.2542273765046458</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.1384804115701109</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.397762064243385</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.1473623819510513</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>2.656789998074496</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>6.038252425337495</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.4139596520279204</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>7.580220584568238</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.615995413294821</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>6.752853694213151</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-9.093131397928103</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.423372544051355</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-10.87003489253777</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-4.998475343120493</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-6.973393012225873</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.8317901359095442</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>14.12063162580987</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>16.29413255732643</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>12.35808057750992</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>16.64418844675642</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>9.271941298216376</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>14.39078394824776</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.2034474254588697</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.4623876599565711</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.03441630201190403</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.6302139826365405</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.1284136689632321</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.5366096411609201</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.5230785434606244</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.2448984933732778</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.6103363833243547</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.287073322016745</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.4175400649071024</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.05948033828129252</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>1.943262673881924</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>2.430848968582862</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>2.072005606795651</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>2.552756537144059</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.9868357475094475</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.93744823478465</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.428793590385294</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-4.237435059736979</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-3.696596475783501</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-2.9819952605946</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-2.546400162331394</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-3.685399460576544</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-6.156119608094677</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-8.633043634768541</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-8.671346887181503</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-7.839189742927134</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-5.803852933867059</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-7.060742156614704</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>3.868110966253546</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.267092272975779</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.336040284398595</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1.651741976461697</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.9969861609338793</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-0.16435501543265</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.07282424335796421</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.215978013955564</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.1815414754145945</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.1464470960880118</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1274399889494005</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.1844436210293007</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.280399789381588</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.4022464925305427</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.3799304196894677</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.3479918259574206</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.2718800050066546</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.3187770133986467</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.2221386765494888</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.01999371915640691</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.07806818432274483</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.09374585093737649</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.05348142980613888</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.009270681631321496</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
